--- a/sample-format/delete_events.xlsx
+++ b/sample-format/delete_events.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mithilesh Thakur\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A7AEAD5-2BEA-479E-9B56-5070B040F456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EF05AA-02BA-47A7-AC10-A631BE4B79D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BFB7F0D1-E7B0-4908-8142-1D92C237B51C}"/>
   </bookViews>
@@ -20,25 +20,571 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="186">
   <si>
     <t>event</t>
   </si>
   <si>
-    <t>pZnoJbYyjMo</t>
-  </si>
-  <si>
-    <t>is1ijOF7zGF</t>
-  </si>
-  <si>
-    <t>USlTQ5ImdB3</t>
+    <t>Jbwmg8U70gk</t>
+  </si>
+  <si>
+    <t>fwqATJrQvx7</t>
+  </si>
+  <si>
+    <t>vTpBLbSp3I1</t>
+  </si>
+  <si>
+    <t>UK7IZzgYMSE</t>
+  </si>
+  <si>
+    <t>ESmq6vKEiL3</t>
+  </si>
+  <si>
+    <t>nd3cSBZZSO9</t>
+  </si>
+  <si>
+    <t>wF9eyNzVDdV</t>
+  </si>
+  <si>
+    <t>jvpjg32CMDd</t>
+  </si>
+  <si>
+    <t>Lk4S8xBh3oy</t>
+  </si>
+  <si>
+    <t>sUtG3LRVVN3</t>
+  </si>
+  <si>
+    <t>ATItQhOU5yu</t>
+  </si>
+  <si>
+    <t>skPV4YuGsnA</t>
+  </si>
+  <si>
+    <t>iZQbqUfuWtD</t>
+  </si>
+  <si>
+    <t>tLCuSp2dBpU</t>
+  </si>
+  <si>
+    <t>B7V18j78pVO</t>
+  </si>
+  <si>
+    <t>TgqOJOkQuyl</t>
+  </si>
+  <si>
+    <t>kxgVHXeQ4r5</t>
+  </si>
+  <si>
+    <t>WZmL9IhnbCA</t>
+  </si>
+  <si>
+    <t>FxT1wndQvjN</t>
+  </si>
+  <si>
+    <t>b9SEWO5UqYy</t>
+  </si>
+  <si>
+    <t>Zx8zdyKZmu1</t>
+  </si>
+  <si>
+    <t>WXJTyIFQDI5</t>
+  </si>
+  <si>
+    <t>aDZ5i0bof3V</t>
+  </si>
+  <si>
+    <t>JZDZimob3qV</t>
+  </si>
+  <si>
+    <t>wGwKyeqc4Sa</t>
+  </si>
+  <si>
+    <t>gqimZZX7Spy</t>
+  </si>
+  <si>
+    <t>aBVlfsfPwQq</t>
+  </si>
+  <si>
+    <t>YNCeRycoy7p</t>
+  </si>
+  <si>
+    <t>epayLAoFUIY</t>
+  </si>
+  <si>
+    <t>Gr2WWit2a8T</t>
+  </si>
+  <si>
+    <t>Hd894kn32S4</t>
+  </si>
+  <si>
+    <t>UJhc2XhsPkD</t>
+  </si>
+  <si>
+    <t>LLEdityQBSv</t>
+  </si>
+  <si>
+    <t>j39M0hJaZDt</t>
+  </si>
+  <si>
+    <t>oOEkLcjWeCC</t>
+  </si>
+  <si>
+    <t>ICsYUr4jNKU</t>
+  </si>
+  <si>
+    <t>G5LXAPZTtuy</t>
+  </si>
+  <si>
+    <t>xq6uMCyOv6d</t>
+  </si>
+  <si>
+    <t>mY2kRvfqZZD</t>
+  </si>
+  <si>
+    <t>AgbWbA1LrVz</t>
+  </si>
+  <si>
+    <t>anpLu57VZBe</t>
+  </si>
+  <si>
+    <t>nqwDzTcWmiG</t>
+  </si>
+  <si>
+    <t>YwgDPqXCihi</t>
+  </si>
+  <si>
+    <t>Tg20pWN2T8u</t>
+  </si>
+  <si>
+    <t>kBQUGe4E0Cm</t>
+  </si>
+  <si>
+    <t>PfKJ0aQt92w</t>
+  </si>
+  <si>
+    <t>b8d2t7maTAb</t>
+  </si>
+  <si>
+    <t>BAqUzCYZlrQ</t>
+  </si>
+  <si>
+    <t>H3h8v4yXKNS</t>
+  </si>
+  <si>
+    <t>yhTVcPhhmhG</t>
+  </si>
+  <si>
+    <t>OfrRv4Ul7Tq</t>
+  </si>
+  <si>
+    <t>L90qebs9qqN</t>
+  </si>
+  <si>
+    <t>mnHh50g2qyb</t>
+  </si>
+  <si>
+    <t>Ds0790UyFRv</t>
+  </si>
+  <si>
+    <t>oZLnUCjdTmr</t>
+  </si>
+  <si>
+    <t>yvNYrlP7OID</t>
+  </si>
+  <si>
+    <t>IXKu29bCOeo</t>
+  </si>
+  <si>
+    <t>QRNeDaflzlH</t>
+  </si>
+  <si>
+    <t>jSOymCpmxq3</t>
+  </si>
+  <si>
+    <t>GJxngauakqm</t>
+  </si>
+  <si>
+    <t>xpJpjioBnaL</t>
+  </si>
+  <si>
+    <t>HKuQAAQMHec</t>
+  </si>
+  <si>
+    <t>XBIj7khiBSQ</t>
+  </si>
+  <si>
+    <t>nHywAIUD0Ah</t>
+  </si>
+  <si>
+    <t>fPEfpKKcgyF</t>
+  </si>
+  <si>
+    <t>V9ZuJgwDUWU</t>
+  </si>
+  <si>
+    <t>xkoIzP2f3k2</t>
+  </si>
+  <si>
+    <t>dpRWlqFQFY8</t>
+  </si>
+  <si>
+    <t>wnYhz47TCNJ</t>
+  </si>
+  <si>
+    <t>hqqVqbSPkma</t>
+  </si>
+  <si>
+    <t>wD3Z8HVV1AI</t>
+  </si>
+  <si>
+    <t>S2WPQkuvC8b</t>
+  </si>
+  <si>
+    <t>tKssjByWbGE</t>
+  </si>
+  <si>
+    <t>FEj3NqjoE4R</t>
+  </si>
+  <si>
+    <t>lnmVfVbcly7</t>
+  </si>
+  <si>
+    <t>LpzcqHS0T2F</t>
+  </si>
+  <si>
+    <t>XcMoOFIKaVu</t>
+  </si>
+  <si>
+    <t>nYLT77bPMTC</t>
+  </si>
+  <si>
+    <t>a8BJFifKB09</t>
+  </si>
+  <si>
+    <t>jPx3jKMqntz</t>
+  </si>
+  <si>
+    <t>XmeyMU3GQ6b</t>
+  </si>
+  <si>
+    <t>PxaZ3oqRetY</t>
+  </si>
+  <si>
+    <t>ILeNTV1yUO8</t>
+  </si>
+  <si>
+    <t>IgazwmXSSu9</t>
+  </si>
+  <si>
+    <t>xIqyMvek7nQ</t>
+  </si>
+  <si>
+    <t>D7JKjfdGPDz</t>
+  </si>
+  <si>
+    <t>o03kykyVGP9</t>
+  </si>
+  <si>
+    <t>lKXO0e1FURa</t>
+  </si>
+  <si>
+    <t>vyItqXXeAq0</t>
+  </si>
+  <si>
+    <t>nV3t5ngdCAk</t>
+  </si>
+  <si>
+    <t>qBEbcvoy71Q</t>
+  </si>
+  <si>
+    <t>uk3XKBJajPR</t>
+  </si>
+  <si>
+    <t>NFcJMrUTcKK</t>
+  </si>
+  <si>
+    <t>Zgg50wsVJtn</t>
+  </si>
+  <si>
+    <t>AaxoXcOmrgM</t>
+  </si>
+  <si>
+    <t>VnCgGgzykOt</t>
+  </si>
+  <si>
+    <t>ZpdxJx2pY0F</t>
+  </si>
+  <si>
+    <t>rsx4fzwEVlY</t>
+  </si>
+  <si>
+    <t>lkafd0cxaYM</t>
+  </si>
+  <si>
+    <t>ENlv2BAORp0</t>
+  </si>
+  <si>
+    <t>rWhoeapvb05</t>
+  </si>
+  <si>
+    <t>kCFbWeyrQBI</t>
+  </si>
+  <si>
+    <t>ECLHWUat3YP</t>
+  </si>
+  <si>
+    <t>kryT7Rs2pAZ</t>
+  </si>
+  <si>
+    <t>PIlsUMKBFU2</t>
+  </si>
+  <si>
+    <t>t8SKwp6MrzB</t>
+  </si>
+  <si>
+    <t>t4vWxL2C1i8</t>
+  </si>
+  <si>
+    <t>aXGQXsfvRdb</t>
+  </si>
+  <si>
+    <t>DOW1WYN2dkk</t>
+  </si>
+  <si>
+    <t>snCSBHnvnVF</t>
+  </si>
+  <si>
+    <t>yRrx74XTY8s</t>
+  </si>
+  <si>
+    <t>Vd0ZtrAZVeU</t>
+  </si>
+  <si>
+    <t>SGFj1bgcUQP</t>
+  </si>
+  <si>
+    <t>JQzshEifg1h</t>
+  </si>
+  <si>
+    <t>IFC9YgaBXu5</t>
+  </si>
+  <si>
+    <t>faFLDlqyGGa</t>
+  </si>
+  <si>
+    <t>qhYLrxLxgZN</t>
+  </si>
+  <si>
+    <t>WYffO8x2Wn6</t>
+  </si>
+  <si>
+    <t>aUvYLumgMKQ</t>
+  </si>
+  <si>
+    <t>RG7QznEjXLI</t>
+  </si>
+  <si>
+    <t>AV67oRPJ24V</t>
+  </si>
+  <si>
+    <t>XHk6g7wwgzH</t>
+  </si>
+  <si>
+    <t>nhNkLNpcJEZ</t>
+  </si>
+  <si>
+    <t>eMpn1nxqCGk</t>
+  </si>
+  <si>
+    <t>edkcACihJJX</t>
+  </si>
+  <si>
+    <t>eWURH71Zcy8</t>
+  </si>
+  <si>
+    <t>VG3s5V42xCW</t>
+  </si>
+  <si>
+    <t>IGadUMBa0AE</t>
+  </si>
+  <si>
+    <t>eZEZi1sauhP</t>
+  </si>
+  <si>
+    <t>hsJKGsJWHhP</t>
+  </si>
+  <si>
+    <t>HctdjHgvrsS</t>
+  </si>
+  <si>
+    <t>bnQeA52pAjA</t>
+  </si>
+  <si>
+    <t>Zk6Yv2vw9EJ</t>
+  </si>
+  <si>
+    <t>VPFxiQKTjgF</t>
+  </si>
+  <si>
+    <t>RWIWvOcPuen</t>
+  </si>
+  <si>
+    <t>XkGrHyhvylQ</t>
+  </si>
+  <si>
+    <t>byMfXe1ZErA</t>
+  </si>
+  <si>
+    <t>EtG4TboJzK5</t>
+  </si>
+  <si>
+    <t>iCJc0xhVNNM</t>
+  </si>
+  <si>
+    <t>CfCRmec45GF</t>
+  </si>
+  <si>
+    <t>wHcPBjYUc7f</t>
+  </si>
+  <si>
+    <t>jhGxFSUk8NV</t>
+  </si>
+  <si>
+    <t>bKE9GjUyD8y</t>
+  </si>
+  <si>
+    <t>msdIzKHrX2v</t>
+  </si>
+  <si>
+    <t>hfa140lfL3p</t>
+  </si>
+  <si>
+    <t>CMLEyQhLpr5</t>
+  </si>
+  <si>
+    <t>D4Y2XdvK9ci</t>
+  </si>
+  <si>
+    <t>kb6IJHewqD9</t>
+  </si>
+  <si>
+    <t>HOevOIvJkHG</t>
+  </si>
+  <si>
+    <t>fs542pWGeAU</t>
+  </si>
+  <si>
+    <t>rClh587FIzH</t>
+  </si>
+  <si>
+    <t>PNdJeUYy85c</t>
+  </si>
+  <si>
+    <t>chaoXLVxR7O</t>
+  </si>
+  <si>
+    <t>cyPF7tst6Ob</t>
+  </si>
+  <si>
+    <t>CNedMgwt4B0</t>
+  </si>
+  <si>
+    <t>yk5LWMtS4lJ</t>
+  </si>
+  <si>
+    <t>qKBxk2pIp0W</t>
+  </si>
+  <si>
+    <t>isJY5UR4TWa</t>
+  </si>
+  <si>
+    <t>RibZ4apTWpc</t>
+  </si>
+  <si>
+    <t>vCsccgUBZux</t>
+  </si>
+  <si>
+    <t>uJ3JTs5Iqrf</t>
+  </si>
+  <si>
+    <t>b6fSqVm2kna</t>
+  </si>
+  <si>
+    <t>BU0VBuQpZgt</t>
+  </si>
+  <si>
+    <t>yDzwxEyWuRQ</t>
+  </si>
+  <si>
+    <t>ri3AZjg8AB3</t>
+  </si>
+  <si>
+    <t>HkenebxWKSB</t>
+  </si>
+  <si>
+    <t>Jhb2DtB6qke</t>
+  </si>
+  <si>
+    <t>QxOAo9ONmfl</t>
+  </si>
+  <si>
+    <t>gmbsMbeZYoI</t>
+  </si>
+  <si>
+    <t>aiK5hC4s0aO</t>
+  </si>
+  <si>
+    <t>AblVZzGdjxd</t>
+  </si>
+  <si>
+    <t>V4mLbn72Tx6</t>
+  </si>
+  <si>
+    <t>nHeJtU9PSre</t>
+  </si>
+  <si>
+    <t>rgH3HRdPwGP</t>
+  </si>
+  <si>
+    <t>eqTT21BcX2U</t>
+  </si>
+  <si>
+    <t>OmFZxpyF905</t>
+  </si>
+  <si>
+    <t>eC8yn3K8VQH</t>
+  </si>
+  <si>
+    <t>YtmOjnnQHGc</t>
+  </si>
+  <si>
+    <t>UVpkV0gh5pF</t>
+  </si>
+  <si>
+    <t>BeCyufAmHaP</t>
+  </si>
+  <si>
+    <t>SEwkj3wTHIC</t>
+  </si>
+  <si>
+    <t>EvxO0Jt0IkY</t>
+  </si>
+  <si>
+    <t>L04s62AzLa1</t>
+  </si>
+  <si>
+    <t>X62UMhqcSk9</t>
+  </si>
+  <si>
+    <t>oPbV4KwM1oO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,11 +728,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -532,12 +1073,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
@@ -914,10 +1454,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{512C072E-A812-4DB2-AAD1-F6BD356A5C97}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C1138"/>
   <sheetFormatPr defaultColWidth="31.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.26953125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.26953125" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="31.81640625" style="1"/>
@@ -929,22 +1469,3788 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="2"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="3" t="s">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3"/>
+      <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A136" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A162" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A163" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A164" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A165" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A166" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A167" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A168" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A169" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A170" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A171" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A172" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A173" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A174" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A175" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A176" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A177" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A178" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A179" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A180" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A181" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A182" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A183" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A184" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A185" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A186" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A187"/>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A188"/>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A189"/>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A190"/>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A191"/>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A192"/>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A193"/>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A194"/>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A195"/>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A196"/>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A197"/>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A198"/>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A199"/>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A200"/>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A201"/>
+    </row>
+    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A202"/>
+    </row>
+    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A203"/>
+    </row>
+    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A204"/>
+    </row>
+    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A205"/>
+    </row>
+    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A206"/>
+    </row>
+    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A207"/>
+    </row>
+    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A208"/>
+    </row>
+    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A209"/>
+    </row>
+    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A210"/>
+    </row>
+    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A211"/>
+    </row>
+    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A212"/>
+    </row>
+    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A213"/>
+    </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A214"/>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A215"/>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A216"/>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A217"/>
+    </row>
+    <row r="218" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A218"/>
+    </row>
+    <row r="219" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A219"/>
+    </row>
+    <row r="220" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A220"/>
+    </row>
+    <row r="221" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A221"/>
+    </row>
+    <row r="222" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A222"/>
+    </row>
+    <row r="223" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A223"/>
+    </row>
+    <row r="224" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A224"/>
+    </row>
+    <row r="225" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A225"/>
+    </row>
+    <row r="226" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A226"/>
+    </row>
+    <row r="227" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A227"/>
+    </row>
+    <row r="228" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A228"/>
+    </row>
+    <row r="229" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A229"/>
+    </row>
+    <row r="230" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A230"/>
+    </row>
+    <row r="231" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A231"/>
+    </row>
+    <row r="232" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A232"/>
+    </row>
+    <row r="233" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A233"/>
+    </row>
+    <row r="234" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A234"/>
+    </row>
+    <row r="235" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A235"/>
+    </row>
+    <row r="236" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A236"/>
+    </row>
+    <row r="237" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A237"/>
+    </row>
+    <row r="238" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A238"/>
+    </row>
+    <row r="239" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A239"/>
+    </row>
+    <row r="240" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A240"/>
+    </row>
+    <row r="241" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A241"/>
+    </row>
+    <row r="242" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A242"/>
+    </row>
+    <row r="243" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A243"/>
+    </row>
+    <row r="244" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A244"/>
+    </row>
+    <row r="245" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A245"/>
+    </row>
+    <row r="246" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A246"/>
+    </row>
+    <row r="247" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A247"/>
+    </row>
+    <row r="248" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A248"/>
+    </row>
+    <row r="249" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A249"/>
+    </row>
+    <row r="250" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A250"/>
+    </row>
+    <row r="251" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A251"/>
+    </row>
+    <row r="252" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A252"/>
+    </row>
+    <row r="253" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A253"/>
+    </row>
+    <row r="254" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A254"/>
+    </row>
+    <row r="255" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A255"/>
+    </row>
+    <row r="256" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A256"/>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A257"/>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A258"/>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A259"/>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A260"/>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A261"/>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A262"/>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A263"/>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A264"/>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A265"/>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A266"/>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A267"/>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A268"/>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A269"/>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A270"/>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A271"/>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A272"/>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A273"/>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A274"/>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A275"/>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A276"/>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A277"/>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A278"/>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A279"/>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A280"/>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A281"/>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A282"/>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A283"/>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A284"/>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A285"/>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A286"/>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A287"/>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A288"/>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A289"/>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A290"/>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A291"/>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A292"/>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A293"/>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A294"/>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A295"/>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A296"/>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A297"/>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A298"/>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A299"/>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A300"/>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A301"/>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A302"/>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A303"/>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A304"/>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A305"/>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A306"/>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A307"/>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A308"/>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A309"/>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A310"/>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A311"/>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A312"/>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A313"/>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A314"/>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A315"/>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A316"/>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A317"/>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A318"/>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A319"/>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A320"/>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A321"/>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A322"/>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A323"/>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A324"/>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A325"/>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A326"/>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A327"/>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A328"/>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A329"/>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A330"/>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A331"/>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A332"/>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A333"/>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A334"/>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A335"/>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A336"/>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A337"/>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A338"/>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A339"/>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A340"/>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A341"/>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A342"/>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A343"/>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A344"/>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A345"/>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A346"/>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A347"/>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A348"/>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A349"/>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A350"/>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A351"/>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A352"/>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A353"/>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A354"/>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A355"/>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A356"/>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A357"/>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A358"/>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A359"/>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A360"/>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A361"/>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A362"/>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A363"/>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A364"/>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A365"/>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A366"/>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A367"/>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A368"/>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A369"/>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A370"/>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A371"/>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A372"/>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A373"/>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A374"/>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A375"/>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A376"/>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A377"/>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A378"/>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A379"/>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A380"/>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A381"/>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A382"/>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A383"/>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A384"/>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A385"/>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A386"/>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A387"/>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A388"/>
+    </row>
+    <row r="389" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A389"/>
+    </row>
+    <row r="390" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A390"/>
+    </row>
+    <row r="391" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A391"/>
+    </row>
+    <row r="392" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A392"/>
+    </row>
+    <row r="393" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A393"/>
+    </row>
+    <row r="394" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A394"/>
+    </row>
+    <row r="395" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A395"/>
+    </row>
+    <row r="396" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A396"/>
+    </row>
+    <row r="397" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A397"/>
+    </row>
+    <row r="398" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A398"/>
+    </row>
+    <row r="399" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A399"/>
+    </row>
+    <row r="400" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A400"/>
+    </row>
+    <row r="401" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A401"/>
+    </row>
+    <row r="402" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A402"/>
+    </row>
+    <row r="403" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A403"/>
+    </row>
+    <row r="404" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A404"/>
+    </row>
+    <row r="405" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A405"/>
+    </row>
+    <row r="406" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A406"/>
+    </row>
+    <row r="407" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A407"/>
+    </row>
+    <row r="408" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A408"/>
+    </row>
+    <row r="409" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A409"/>
+    </row>
+    <row r="410" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A410"/>
+    </row>
+    <row r="411" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A411"/>
+    </row>
+    <row r="412" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A412"/>
+    </row>
+    <row r="413" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A413"/>
+    </row>
+    <row r="414" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A414"/>
+    </row>
+    <row r="415" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A415"/>
+    </row>
+    <row r="416" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A416"/>
+    </row>
+    <row r="417" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A417"/>
+    </row>
+    <row r="418" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A418"/>
+    </row>
+    <row r="419" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A419"/>
+    </row>
+    <row r="420" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A420"/>
+    </row>
+    <row r="421" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A421"/>
+    </row>
+    <row r="422" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A422"/>
+    </row>
+    <row r="423" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A423"/>
+    </row>
+    <row r="424" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A424"/>
+    </row>
+    <row r="425" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A425"/>
+    </row>
+    <row r="426" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A426"/>
+    </row>
+    <row r="427" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A427"/>
+    </row>
+    <row r="428" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A428"/>
+    </row>
+    <row r="429" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A429"/>
+    </row>
+    <row r="430" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A430"/>
+    </row>
+    <row r="431" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A431"/>
+    </row>
+    <row r="432" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A432"/>
+    </row>
+    <row r="433" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A433"/>
+    </row>
+    <row r="434" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A434"/>
+    </row>
+    <row r="435" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A435"/>
+    </row>
+    <row r="436" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A436"/>
+    </row>
+    <row r="437" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A437"/>
+    </row>
+    <row r="438" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A438"/>
+    </row>
+    <row r="439" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A439"/>
+    </row>
+    <row r="440" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A440"/>
+    </row>
+    <row r="441" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A441"/>
+    </row>
+    <row r="442" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A442"/>
+    </row>
+    <row r="443" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A443"/>
+    </row>
+    <row r="444" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A444"/>
+    </row>
+    <row r="445" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A445"/>
+    </row>
+    <row r="446" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A446"/>
+    </row>
+    <row r="447" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A447"/>
+    </row>
+    <row r="448" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A448"/>
+    </row>
+    <row r="449" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A449"/>
+    </row>
+    <row r="450" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A450"/>
+    </row>
+    <row r="451" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A451"/>
+    </row>
+    <row r="452" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A452"/>
+    </row>
+    <row r="453" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A453"/>
+    </row>
+    <row r="454" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A454"/>
+    </row>
+    <row r="455" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A455"/>
+    </row>
+    <row r="456" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A456"/>
+    </row>
+    <row r="457" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A457"/>
+    </row>
+    <row r="458" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A458"/>
+    </row>
+    <row r="459" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A459"/>
+    </row>
+    <row r="460" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A460"/>
+    </row>
+    <row r="461" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A461"/>
+    </row>
+    <row r="462" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A462"/>
+    </row>
+    <row r="463" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A463"/>
+    </row>
+    <row r="464" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A464"/>
+    </row>
+    <row r="465" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A465"/>
+    </row>
+    <row r="466" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A466"/>
+    </row>
+    <row r="467" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A467"/>
+    </row>
+    <row r="468" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A468"/>
+    </row>
+    <row r="469" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A469"/>
+    </row>
+    <row r="470" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A470"/>
+    </row>
+    <row r="471" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A471"/>
+    </row>
+    <row r="472" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A472"/>
+    </row>
+    <row r="473" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A473"/>
+    </row>
+    <row r="474" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A474"/>
+    </row>
+    <row r="475" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A475"/>
+    </row>
+    <row r="476" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A476"/>
+    </row>
+    <row r="477" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A477"/>
+    </row>
+    <row r="478" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A478"/>
+    </row>
+    <row r="479" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A479"/>
+    </row>
+    <row r="480" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A480"/>
+    </row>
+    <row r="481" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A481"/>
+    </row>
+    <row r="482" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A482"/>
+    </row>
+    <row r="483" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A483"/>
+    </row>
+    <row r="484" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A484"/>
+    </row>
+    <row r="485" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A485"/>
+    </row>
+    <row r="486" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A486"/>
+    </row>
+    <row r="487" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A487"/>
+    </row>
+    <row r="488" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A488"/>
+    </row>
+    <row r="489" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A489"/>
+    </row>
+    <row r="490" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A490"/>
+    </row>
+    <row r="491" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A491"/>
+    </row>
+    <row r="492" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A492"/>
+    </row>
+    <row r="493" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A493"/>
+    </row>
+    <row r="494" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A494"/>
+    </row>
+    <row r="495" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A495"/>
+    </row>
+    <row r="496" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A496"/>
+    </row>
+    <row r="497" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A497"/>
+    </row>
+    <row r="498" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A498"/>
+    </row>
+    <row r="499" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A499"/>
+    </row>
+    <row r="500" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A500"/>
+    </row>
+    <row r="501" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A501"/>
+    </row>
+    <row r="502" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A502"/>
+    </row>
+    <row r="503" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A503"/>
+    </row>
+    <row r="504" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A504"/>
+    </row>
+    <row r="505" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A505"/>
+    </row>
+    <row r="506" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A506"/>
+    </row>
+    <row r="507" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A507"/>
+    </row>
+    <row r="508" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A508"/>
+    </row>
+    <row r="509" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A509"/>
+    </row>
+    <row r="510" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A510"/>
+    </row>
+    <row r="511" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A511"/>
+    </row>
+    <row r="512" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A512"/>
+    </row>
+    <row r="513" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A513"/>
+    </row>
+    <row r="514" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A514"/>
+    </row>
+    <row r="515" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A515"/>
+    </row>
+    <row r="516" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A516"/>
+    </row>
+    <row r="517" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A517"/>
+    </row>
+    <row r="518" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A518"/>
+    </row>
+    <row r="519" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A519"/>
+    </row>
+    <row r="520" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A520"/>
+    </row>
+    <row r="521" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A521"/>
+    </row>
+    <row r="522" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A522"/>
+    </row>
+    <row r="523" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A523"/>
+    </row>
+    <row r="524" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A524"/>
+    </row>
+    <row r="525" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A525"/>
+    </row>
+    <row r="526" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A526"/>
+    </row>
+    <row r="527" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A527"/>
+    </row>
+    <row r="528" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A528"/>
+    </row>
+    <row r="529" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A529"/>
+    </row>
+    <row r="530" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A530"/>
+    </row>
+    <row r="531" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A531"/>
+    </row>
+    <row r="532" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A532"/>
+    </row>
+    <row r="533" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A533"/>
+    </row>
+    <row r="534" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A534"/>
+    </row>
+    <row r="535" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A535"/>
+    </row>
+    <row r="536" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A536"/>
+    </row>
+    <row r="537" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A537"/>
+    </row>
+    <row r="538" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A538"/>
+    </row>
+    <row r="539" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A539"/>
+    </row>
+    <row r="540" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A540"/>
+    </row>
+    <row r="541" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A541"/>
+    </row>
+    <row r="542" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A542"/>
+    </row>
+    <row r="543" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A543"/>
+    </row>
+    <row r="544" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A544"/>
+    </row>
+    <row r="545" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A545"/>
+    </row>
+    <row r="546" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A546"/>
+    </row>
+    <row r="547" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A547"/>
+    </row>
+    <row r="548" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A548"/>
+    </row>
+    <row r="549" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A549"/>
+    </row>
+    <row r="550" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A550"/>
+    </row>
+    <row r="551" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A551"/>
+    </row>
+    <row r="552" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A552"/>
+    </row>
+    <row r="553" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A553"/>
+    </row>
+    <row r="554" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A554"/>
+    </row>
+    <row r="555" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A555"/>
+    </row>
+    <row r="556" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A556"/>
+    </row>
+    <row r="557" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A557"/>
+    </row>
+    <row r="558" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A558"/>
+    </row>
+    <row r="559" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A559"/>
+    </row>
+    <row r="560" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A560"/>
+    </row>
+    <row r="561" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A561"/>
+    </row>
+    <row r="562" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A562"/>
+    </row>
+    <row r="563" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A563"/>
+    </row>
+    <row r="564" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A564"/>
+    </row>
+    <row r="565" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A565"/>
+    </row>
+    <row r="566" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A566"/>
+    </row>
+    <row r="567" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A567"/>
+    </row>
+    <row r="568" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A568"/>
+    </row>
+    <row r="569" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A569"/>
+    </row>
+    <row r="570" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A570"/>
+    </row>
+    <row r="571" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A571"/>
+    </row>
+    <row r="572" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A572"/>
+    </row>
+    <row r="573" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A573"/>
+    </row>
+    <row r="574" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A574"/>
+    </row>
+    <row r="575" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A575"/>
+    </row>
+    <row r="576" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A576"/>
+    </row>
+    <row r="577" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A577"/>
+    </row>
+    <row r="578" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A578"/>
+    </row>
+    <row r="579" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A579"/>
+    </row>
+    <row r="580" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A580"/>
+    </row>
+    <row r="581" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A581"/>
+    </row>
+    <row r="582" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A582"/>
+    </row>
+    <row r="583" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A583"/>
+    </row>
+    <row r="584" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A584"/>
+    </row>
+    <row r="585" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A585"/>
+    </row>
+    <row r="586" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A586"/>
+    </row>
+    <row r="587" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A587"/>
+    </row>
+    <row r="588" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A588"/>
+    </row>
+    <row r="589" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A589"/>
+    </row>
+    <row r="590" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A590"/>
+    </row>
+    <row r="591" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A591"/>
+    </row>
+    <row r="592" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A592"/>
+    </row>
+    <row r="593" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A593"/>
+    </row>
+    <row r="594" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A594"/>
+    </row>
+    <row r="595" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A595"/>
+    </row>
+    <row r="596" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A596"/>
+    </row>
+    <row r="597" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A597"/>
+    </row>
+    <row r="598" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A598"/>
+    </row>
+    <row r="599" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A599"/>
+    </row>
+    <row r="600" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A600"/>
+    </row>
+    <row r="601" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A601"/>
+    </row>
+    <row r="602" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A602"/>
+    </row>
+    <row r="603" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A603"/>
+    </row>
+    <row r="604" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A604"/>
+    </row>
+    <row r="605" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A605"/>
+    </row>
+    <row r="606" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A606"/>
+    </row>
+    <row r="607" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A607"/>
+    </row>
+    <row r="608" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A608"/>
+    </row>
+    <row r="609" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A609"/>
+    </row>
+    <row r="610" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A610"/>
+    </row>
+    <row r="611" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A611"/>
+    </row>
+    <row r="612" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A612"/>
+    </row>
+    <row r="613" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A613"/>
+    </row>
+    <row r="614" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A614"/>
+    </row>
+    <row r="615" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A615"/>
+    </row>
+    <row r="616" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A616"/>
+    </row>
+    <row r="617" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A617"/>
+    </row>
+    <row r="618" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A618"/>
+    </row>
+    <row r="619" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A619"/>
+    </row>
+    <row r="620" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A620"/>
+    </row>
+    <row r="621" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A621"/>
+    </row>
+    <row r="622" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A622"/>
+    </row>
+    <row r="623" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A623"/>
+    </row>
+    <row r="624" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A624"/>
+    </row>
+    <row r="625" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A625"/>
+    </row>
+    <row r="626" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A626"/>
+    </row>
+    <row r="627" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A627"/>
+    </row>
+    <row r="628" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A628"/>
+    </row>
+    <row r="629" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A629"/>
+    </row>
+    <row r="630" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A630"/>
+    </row>
+    <row r="631" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A631"/>
+    </row>
+    <row r="632" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A632"/>
+    </row>
+    <row r="633" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A633"/>
+    </row>
+    <row r="634" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A634"/>
+    </row>
+    <row r="635" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A635"/>
+    </row>
+    <row r="636" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A636"/>
+    </row>
+    <row r="637" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A637"/>
+    </row>
+    <row r="638" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A638"/>
+    </row>
+    <row r="639" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A639"/>
+    </row>
+    <row r="640" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A640"/>
+    </row>
+    <row r="641" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A641"/>
+    </row>
+    <row r="642" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A642"/>
+    </row>
+    <row r="643" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A643"/>
+    </row>
+    <row r="644" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A644"/>
+    </row>
+    <row r="645" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A645"/>
+    </row>
+    <row r="646" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A646"/>
+    </row>
+    <row r="647" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A647"/>
+    </row>
+    <row r="648" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A648"/>
+    </row>
+    <row r="649" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A649"/>
+    </row>
+    <row r="650" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A650"/>
+    </row>
+    <row r="651" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A651"/>
+    </row>
+    <row r="652" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A652"/>
+    </row>
+    <row r="653" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A653"/>
+    </row>
+    <row r="654" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A654"/>
+    </row>
+    <row r="655" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A655"/>
+    </row>
+    <row r="656" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A656"/>
+    </row>
+    <row r="657" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A657"/>
+    </row>
+    <row r="658" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A658"/>
+    </row>
+    <row r="659" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A659"/>
+    </row>
+    <row r="660" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A660"/>
+    </row>
+    <row r="661" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A661"/>
+    </row>
+    <row r="662" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A662"/>
+    </row>
+    <row r="663" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A663"/>
+    </row>
+    <row r="664" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A664"/>
+    </row>
+    <row r="665" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A665"/>
+    </row>
+    <row r="666" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A666"/>
+    </row>
+    <row r="667" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A667"/>
+    </row>
+    <row r="668" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A668"/>
+    </row>
+    <row r="669" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A669"/>
+    </row>
+    <row r="670" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A670"/>
+    </row>
+    <row r="671" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A671"/>
+    </row>
+    <row r="672" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A672"/>
+    </row>
+    <row r="673" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A673"/>
+    </row>
+    <row r="674" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A674"/>
+    </row>
+    <row r="675" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A675"/>
+    </row>
+    <row r="676" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A676"/>
+    </row>
+    <row r="677" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A677"/>
+    </row>
+    <row r="678" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A678"/>
+    </row>
+    <row r="679" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A679"/>
+    </row>
+    <row r="680" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A680"/>
+    </row>
+    <row r="681" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A681"/>
+    </row>
+    <row r="682" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A682"/>
+    </row>
+    <row r="683" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A683"/>
+    </row>
+    <row r="684" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A684"/>
+    </row>
+    <row r="685" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A685"/>
+    </row>
+    <row r="686" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A686"/>
+    </row>
+    <row r="687" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A687"/>
+    </row>
+    <row r="688" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A688"/>
+    </row>
+    <row r="689" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A689"/>
+    </row>
+    <row r="690" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A690"/>
+    </row>
+    <row r="691" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A691"/>
+    </row>
+    <row r="692" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A692"/>
+    </row>
+    <row r="693" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A693"/>
+    </row>
+    <row r="694" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A694"/>
+    </row>
+    <row r="695" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A695"/>
+    </row>
+    <row r="696" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A696"/>
+    </row>
+    <row r="697" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A697"/>
+    </row>
+    <row r="698" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A698"/>
+    </row>
+    <row r="699" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A699"/>
+    </row>
+    <row r="700" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A700"/>
+    </row>
+    <row r="701" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A701"/>
+    </row>
+    <row r="702" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A702"/>
+    </row>
+    <row r="703" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A703"/>
+    </row>
+    <row r="704" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A704"/>
+    </row>
+    <row r="705" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A705"/>
+    </row>
+    <row r="706" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A706"/>
+    </row>
+    <row r="707" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A707"/>
+    </row>
+    <row r="708" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A708"/>
+    </row>
+    <row r="709" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A709"/>
+    </row>
+    <row r="710" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A710"/>
+    </row>
+    <row r="711" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A711"/>
+    </row>
+    <row r="712" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A712"/>
+    </row>
+    <row r="713" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A713"/>
+    </row>
+    <row r="714" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A714"/>
+    </row>
+    <row r="715" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A715"/>
+    </row>
+    <row r="716" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A716"/>
+    </row>
+    <row r="717" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A717"/>
+    </row>
+    <row r="718" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A718"/>
+    </row>
+    <row r="719" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A719"/>
+    </row>
+    <row r="720" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A720"/>
+    </row>
+    <row r="721" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A721"/>
+    </row>
+    <row r="722" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A722"/>
+    </row>
+    <row r="723" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A723"/>
+    </row>
+    <row r="724" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A724"/>
+    </row>
+    <row r="725" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A725"/>
+    </row>
+    <row r="726" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A726"/>
+    </row>
+    <row r="727" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A727"/>
+    </row>
+    <row r="728" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A728"/>
+    </row>
+    <row r="729" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A729"/>
+    </row>
+    <row r="730" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A730"/>
+    </row>
+    <row r="731" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A731"/>
+    </row>
+    <row r="732" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A732"/>
+    </row>
+    <row r="733" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A733"/>
+    </row>
+    <row r="734" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A734"/>
+    </row>
+    <row r="735" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A735"/>
+    </row>
+    <row r="736" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A736"/>
+    </row>
+    <row r="737" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A737"/>
+    </row>
+    <row r="738" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A738"/>
+    </row>
+    <row r="739" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A739"/>
+    </row>
+    <row r="740" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A740"/>
+    </row>
+    <row r="741" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A741"/>
+    </row>
+    <row r="742" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A742"/>
+    </row>
+    <row r="743" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A743"/>
+    </row>
+    <row r="744" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A744"/>
+    </row>
+    <row r="745" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A745"/>
+    </row>
+    <row r="746" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A746"/>
+    </row>
+    <row r="747" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A747"/>
+    </row>
+    <row r="748" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A748"/>
+    </row>
+    <row r="749" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A749"/>
+    </row>
+    <row r="750" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A750"/>
+    </row>
+    <row r="751" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A751"/>
+    </row>
+    <row r="752" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A752"/>
+    </row>
+    <row r="753" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A753"/>
+    </row>
+    <row r="754" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A754"/>
+    </row>
+    <row r="755" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A755"/>
+    </row>
+    <row r="756" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A756"/>
+    </row>
+    <row r="757" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A757"/>
+    </row>
+    <row r="758" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A758"/>
+    </row>
+    <row r="759" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A759"/>
+    </row>
+    <row r="760" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A760"/>
+    </row>
+    <row r="761" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A761"/>
+    </row>
+    <row r="762" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A762"/>
+    </row>
+    <row r="763" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A763"/>
+    </row>
+    <row r="764" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A764"/>
+    </row>
+    <row r="765" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A765"/>
+    </row>
+    <row r="766" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A766"/>
+    </row>
+    <row r="767" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A767"/>
+    </row>
+    <row r="768" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A768"/>
+    </row>
+    <row r="769" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A769"/>
+    </row>
+    <row r="770" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A770"/>
+    </row>
+    <row r="771" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A771"/>
+    </row>
+    <row r="772" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A772"/>
+    </row>
+    <row r="773" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A773"/>
+    </row>
+    <row r="774" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A774"/>
+    </row>
+    <row r="775" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A775"/>
+    </row>
+    <row r="776" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A776"/>
+    </row>
+    <row r="777" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A777"/>
+    </row>
+    <row r="778" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A778"/>
+    </row>
+    <row r="779" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A779"/>
+    </row>
+    <row r="780" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A780"/>
+    </row>
+    <row r="781" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A781"/>
+    </row>
+    <row r="782" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A782"/>
+    </row>
+    <row r="783" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A783"/>
+    </row>
+    <row r="784" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A784"/>
+    </row>
+    <row r="785" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A785"/>
+    </row>
+    <row r="786" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A786"/>
+    </row>
+    <row r="787" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A787"/>
+    </row>
+    <row r="788" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A788"/>
+    </row>
+    <row r="789" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A789"/>
+    </row>
+    <row r="790" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A790"/>
+    </row>
+    <row r="791" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A791"/>
+    </row>
+    <row r="792" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A792"/>
+    </row>
+    <row r="793" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A793"/>
+    </row>
+    <row r="794" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A794"/>
+    </row>
+    <row r="795" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A795"/>
+    </row>
+    <row r="796" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A796"/>
+    </row>
+    <row r="797" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A797"/>
+    </row>
+    <row r="798" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A798"/>
+    </row>
+    <row r="799" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A799"/>
+    </row>
+    <row r="800" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A800"/>
+    </row>
+    <row r="801" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A801"/>
+    </row>
+    <row r="802" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A802"/>
+    </row>
+    <row r="803" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A803"/>
+    </row>
+    <row r="804" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A804"/>
+    </row>
+    <row r="805" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A805"/>
+    </row>
+    <row r="806" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A806"/>
+    </row>
+    <row r="807" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A807"/>
+    </row>
+    <row r="808" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A808"/>
+    </row>
+    <row r="809" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A809"/>
+    </row>
+    <row r="810" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A810"/>
+    </row>
+    <row r="811" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A811"/>
+    </row>
+    <row r="812" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A812"/>
+    </row>
+    <row r="813" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A813"/>
+    </row>
+    <row r="814" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A814"/>
+    </row>
+    <row r="815" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A815"/>
+    </row>
+    <row r="816" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A816"/>
+    </row>
+    <row r="817" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A817"/>
+    </row>
+    <row r="818" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A818"/>
+    </row>
+    <row r="819" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A819"/>
+    </row>
+    <row r="820" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A820"/>
+    </row>
+    <row r="821" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A821"/>
+    </row>
+    <row r="822" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A822"/>
+    </row>
+    <row r="823" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A823"/>
+    </row>
+    <row r="824" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A824"/>
+    </row>
+    <row r="825" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A825"/>
+    </row>
+    <row r="826" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A826"/>
+    </row>
+    <row r="827" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A827"/>
+    </row>
+    <row r="828" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A828"/>
+    </row>
+    <row r="829" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A829"/>
+    </row>
+    <row r="830" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A830"/>
+    </row>
+    <row r="831" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A831"/>
+    </row>
+    <row r="832" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A832"/>
+    </row>
+    <row r="833" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A833"/>
+    </row>
+    <row r="834" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A834"/>
+    </row>
+    <row r="835" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A835"/>
+    </row>
+    <row r="836" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A836"/>
+    </row>
+    <row r="837" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A837"/>
+    </row>
+    <row r="838" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A838"/>
+    </row>
+    <row r="839" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A839"/>
+    </row>
+    <row r="840" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A840"/>
+    </row>
+    <row r="841" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A841"/>
+    </row>
+    <row r="842" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A842"/>
+    </row>
+    <row r="843" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A843"/>
+    </row>
+    <row r="844" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A844"/>
+    </row>
+    <row r="845" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A845"/>
+    </row>
+    <row r="846" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A846"/>
+    </row>
+    <row r="847" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A847"/>
+    </row>
+    <row r="848" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A848"/>
+    </row>
+    <row r="849" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A849"/>
+    </row>
+    <row r="850" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A850"/>
+    </row>
+    <row r="851" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A851"/>
+    </row>
+    <row r="852" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A852"/>
+    </row>
+    <row r="853" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A853"/>
+    </row>
+    <row r="854" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A854"/>
+    </row>
+    <row r="855" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A855"/>
+    </row>
+    <row r="856" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A856"/>
+    </row>
+    <row r="857" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A857"/>
+    </row>
+    <row r="858" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A858"/>
+    </row>
+    <row r="859" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A859"/>
+    </row>
+    <row r="860" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A860"/>
+    </row>
+    <row r="861" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A861"/>
+    </row>
+    <row r="862" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A862"/>
+    </row>
+    <row r="863" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A863"/>
+    </row>
+    <row r="864" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A864"/>
+    </row>
+    <row r="865" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A865"/>
+    </row>
+    <row r="866" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A866"/>
+    </row>
+    <row r="867" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A867"/>
+    </row>
+    <row r="868" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A868"/>
+    </row>
+    <row r="869" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A869"/>
+    </row>
+    <row r="870" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A870"/>
+    </row>
+    <row r="871" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A871"/>
+    </row>
+    <row r="872" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A872"/>
+    </row>
+    <row r="873" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A873"/>
+    </row>
+    <row r="874" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A874"/>
+    </row>
+    <row r="875" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A875"/>
+    </row>
+    <row r="876" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A876"/>
+    </row>
+    <row r="877" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A877"/>
+    </row>
+    <row r="878" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A878"/>
+    </row>
+    <row r="879" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A879"/>
+    </row>
+    <row r="880" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A880"/>
+    </row>
+    <row r="881" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A881"/>
+    </row>
+    <row r="882" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A882"/>
+    </row>
+    <row r="883" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A883"/>
+    </row>
+    <row r="884" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A884"/>
+    </row>
+    <row r="885" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A885"/>
+    </row>
+    <row r="886" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A886"/>
+    </row>
+    <row r="887" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A887"/>
+    </row>
+    <row r="888" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A888"/>
+    </row>
+    <row r="889" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A889"/>
+    </row>
+    <row r="890" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A890"/>
+    </row>
+    <row r="891" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A891"/>
+    </row>
+    <row r="892" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A892"/>
+    </row>
+    <row r="893" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A893"/>
+    </row>
+    <row r="894" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A894"/>
+    </row>
+    <row r="895" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A895"/>
+    </row>
+    <row r="896" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A896"/>
+    </row>
+    <row r="897" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A897"/>
+    </row>
+    <row r="898" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A898"/>
+    </row>
+    <row r="899" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A899"/>
+    </row>
+    <row r="900" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A900"/>
+    </row>
+    <row r="901" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A901"/>
+    </row>
+    <row r="902" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A902"/>
+    </row>
+    <row r="903" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A903"/>
+    </row>
+    <row r="904" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A904"/>
+    </row>
+    <row r="905" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A905"/>
+    </row>
+    <row r="906" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A906"/>
+    </row>
+    <row r="907" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A907"/>
+    </row>
+    <row r="908" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A908"/>
+    </row>
+    <row r="909" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A909"/>
+    </row>
+    <row r="910" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A910"/>
+    </row>
+    <row r="911" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A911"/>
+    </row>
+    <row r="912" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A912"/>
+    </row>
+    <row r="913" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A913"/>
+    </row>
+    <row r="914" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A914"/>
+    </row>
+    <row r="915" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A915"/>
+    </row>
+    <row r="916" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A916"/>
+    </row>
+    <row r="917" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A917"/>
+    </row>
+    <row r="918" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A918"/>
+    </row>
+    <row r="919" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A919"/>
+    </row>
+    <row r="920" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A920"/>
+    </row>
+    <row r="921" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A921"/>
+    </row>
+    <row r="922" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A922"/>
+    </row>
+    <row r="923" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A923"/>
+    </row>
+    <row r="924" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A924"/>
+    </row>
+    <row r="925" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A925"/>
+    </row>
+    <row r="926" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A926"/>
+    </row>
+    <row r="927" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A927"/>
+    </row>
+    <row r="928" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A928"/>
+    </row>
+    <row r="929" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A929"/>
+    </row>
+    <row r="930" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A930"/>
+    </row>
+    <row r="931" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A931"/>
+    </row>
+    <row r="932" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A932"/>
+    </row>
+    <row r="933" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A933"/>
+    </row>
+    <row r="934" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A934"/>
+    </row>
+    <row r="935" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A935"/>
+    </row>
+    <row r="936" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A936"/>
+    </row>
+    <row r="937" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A937"/>
+    </row>
+    <row r="938" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A938"/>
+    </row>
+    <row r="939" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A939"/>
+    </row>
+    <row r="940" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A940"/>
+    </row>
+    <row r="941" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A941"/>
+    </row>
+    <row r="942" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A942"/>
+    </row>
+    <row r="943" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A943"/>
+    </row>
+    <row r="944" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A944"/>
+    </row>
+    <row r="945" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A945"/>
+    </row>
+    <row r="946" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A946"/>
+    </row>
+    <row r="947" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A947"/>
+    </row>
+    <row r="948" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A948"/>
+    </row>
+    <row r="949" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A949"/>
+    </row>
+    <row r="950" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A950"/>
+    </row>
+    <row r="951" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A951"/>
+    </row>
+    <row r="952" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A952"/>
+    </row>
+    <row r="953" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A953"/>
+    </row>
+    <row r="954" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A954"/>
+    </row>
+    <row r="955" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A955"/>
+    </row>
+    <row r="956" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A956"/>
+    </row>
+    <row r="957" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A957"/>
+    </row>
+    <row r="958" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A958"/>
+    </row>
+    <row r="959" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A959"/>
+    </row>
+    <row r="960" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A960"/>
+    </row>
+    <row r="961" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A961"/>
+    </row>
+    <row r="962" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A962"/>
+    </row>
+    <row r="963" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A963"/>
+    </row>
+    <row r="964" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A964"/>
+    </row>
+    <row r="965" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A965"/>
+    </row>
+    <row r="966" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A966"/>
+    </row>
+    <row r="967" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A967"/>
+    </row>
+    <row r="968" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A968"/>
+    </row>
+    <row r="969" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A969"/>
+    </row>
+    <row r="970" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A970"/>
+    </row>
+    <row r="971" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A971"/>
+    </row>
+    <row r="972" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A972"/>
+    </row>
+    <row r="973" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A973"/>
+    </row>
+    <row r="974" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A974"/>
+    </row>
+    <row r="975" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A975"/>
+    </row>
+    <row r="976" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A976"/>
+    </row>
+    <row r="977" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A977"/>
+    </row>
+    <row r="978" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A978"/>
+    </row>
+    <row r="979" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A979"/>
+    </row>
+    <row r="980" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A980"/>
+    </row>
+    <row r="981" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A981"/>
+    </row>
+    <row r="982" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A982"/>
+    </row>
+    <row r="983" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A983"/>
+    </row>
+    <row r="984" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A984"/>
+    </row>
+    <row r="985" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A985"/>
+    </row>
+    <row r="986" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A986"/>
+    </row>
+    <row r="987" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A987"/>
+    </row>
+    <row r="988" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A988"/>
+    </row>
+    <row r="989" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A989"/>
+    </row>
+    <row r="990" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A990"/>
+    </row>
+    <row r="991" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A991"/>
+    </row>
+    <row r="992" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A992"/>
+    </row>
+    <row r="993" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A993"/>
+    </row>
+    <row r="994" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A994"/>
+    </row>
+    <row r="995" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A995"/>
+    </row>
+    <row r="996" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A996"/>
+    </row>
+    <row r="997" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A997"/>
+    </row>
+    <row r="998" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A998"/>
+    </row>
+    <row r="999" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A999"/>
+    </row>
+    <row r="1000" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1000"/>
+    </row>
+    <row r="1001" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1001"/>
+    </row>
+    <row r="1002" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1002"/>
+    </row>
+    <row r="1003" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1003"/>
+    </row>
+    <row r="1004" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1004"/>
+    </row>
+    <row r="1005" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1005"/>
+    </row>
+    <row r="1006" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1006"/>
+    </row>
+    <row r="1007" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1007"/>
+    </row>
+    <row r="1008" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1008"/>
+    </row>
+    <row r="1009" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1009"/>
+    </row>
+    <row r="1010" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1010"/>
+    </row>
+    <row r="1011" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1011"/>
+    </row>
+    <row r="1012" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1012"/>
+    </row>
+    <row r="1013" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1013"/>
+    </row>
+    <row r="1014" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1014"/>
+    </row>
+    <row r="1015" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1015"/>
+    </row>
+    <row r="1016" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1016"/>
+    </row>
+    <row r="1017" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1017"/>
+    </row>
+    <row r="1018" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1018"/>
+    </row>
+    <row r="1019" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1019"/>
+    </row>
+    <row r="1020" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1020"/>
+    </row>
+    <row r="1021" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1021"/>
+    </row>
+    <row r="1022" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1022"/>
+    </row>
+    <row r="1023" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1023"/>
+    </row>
+    <row r="1024" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1024"/>
+    </row>
+    <row r="1025" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1025"/>
+    </row>
+    <row r="1026" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1026"/>
+    </row>
+    <row r="1027" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1027"/>
+    </row>
+    <row r="1028" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1028"/>
+    </row>
+    <row r="1029" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1029"/>
+    </row>
+    <row r="1030" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1030"/>
+    </row>
+    <row r="1031" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1031"/>
+    </row>
+    <row r="1032" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1032"/>
+    </row>
+    <row r="1033" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1033"/>
+    </row>
+    <row r="1034" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1034"/>
+    </row>
+    <row r="1035" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1035"/>
+    </row>
+    <row r="1036" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1036"/>
+    </row>
+    <row r="1037" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1037"/>
+    </row>
+    <row r="1038" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1038"/>
+    </row>
+    <row r="1039" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1039"/>
+    </row>
+    <row r="1040" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1040"/>
+    </row>
+    <row r="1041" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1041"/>
+    </row>
+    <row r="1042" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1042"/>
+    </row>
+    <row r="1043" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1043"/>
+    </row>
+    <row r="1044" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1044"/>
+    </row>
+    <row r="1045" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1045"/>
+    </row>
+    <row r="1046" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1046"/>
+    </row>
+    <row r="1047" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1047"/>
+    </row>
+    <row r="1048" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1048"/>
+    </row>
+    <row r="1049" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1049"/>
+    </row>
+    <row r="1050" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1050"/>
+    </row>
+    <row r="1051" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1051"/>
+    </row>
+    <row r="1052" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1052"/>
+    </row>
+    <row r="1053" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1053"/>
+    </row>
+    <row r="1054" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1054"/>
+    </row>
+    <row r="1055" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1055"/>
+    </row>
+    <row r="1056" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1056"/>
+    </row>
+    <row r="1057" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1057"/>
+    </row>
+    <row r="1058" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1058"/>
+    </row>
+    <row r="1059" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1059"/>
+    </row>
+    <row r="1060" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1060"/>
+    </row>
+    <row r="1061" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1061"/>
+    </row>
+    <row r="1062" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1062"/>
+    </row>
+    <row r="1063" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1063"/>
+    </row>
+    <row r="1064" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1064"/>
+    </row>
+    <row r="1065" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1065"/>
+    </row>
+    <row r="1066" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1066"/>
+    </row>
+    <row r="1067" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1067"/>
+    </row>
+    <row r="1068" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1068"/>
+    </row>
+    <row r="1069" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1069"/>
+    </row>
+    <row r="1070" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1070"/>
+    </row>
+    <row r="1071" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1071"/>
+    </row>
+    <row r="1072" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1072"/>
+    </row>
+    <row r="1073" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1073"/>
+    </row>
+    <row r="1074" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1074"/>
+    </row>
+    <row r="1075" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1075"/>
+    </row>
+    <row r="1076" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1076"/>
+    </row>
+    <row r="1077" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1077"/>
+    </row>
+    <row r="1078" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1078"/>
+    </row>
+    <row r="1079" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1079"/>
+    </row>
+    <row r="1080" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1080"/>
+    </row>
+    <row r="1081" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1081"/>
+    </row>
+    <row r="1082" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1082"/>
+    </row>
+    <row r="1083" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1083"/>
+    </row>
+    <row r="1084" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1084"/>
+    </row>
+    <row r="1085" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1085"/>
+    </row>
+    <row r="1086" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1086"/>
+    </row>
+    <row r="1087" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1087"/>
+    </row>
+    <row r="1088" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1088"/>
+    </row>
+    <row r="1089" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1089"/>
+    </row>
+    <row r="1090" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1090"/>
+    </row>
+    <row r="1091" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1091"/>
+    </row>
+    <row r="1092" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1092"/>
+    </row>
+    <row r="1093" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1093"/>
+    </row>
+    <row r="1094" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1094"/>
+    </row>
+    <row r="1095" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1095"/>
+    </row>
+    <row r="1096" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1096"/>
+    </row>
+    <row r="1097" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1097"/>
+    </row>
+    <row r="1098" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1098"/>
+    </row>
+    <row r="1099" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1099"/>
+    </row>
+    <row r="1100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1100"/>
+    </row>
+    <row r="1101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1101"/>
+    </row>
+    <row r="1102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1102"/>
+    </row>
+    <row r="1103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1103"/>
+    </row>
+    <row r="1104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1104"/>
+    </row>
+    <row r="1105" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1105"/>
+    </row>
+    <row r="1106" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1106"/>
+    </row>
+    <row r="1107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1107"/>
+    </row>
+    <row r="1108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1108"/>
+    </row>
+    <row r="1109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1109"/>
+    </row>
+    <row r="1110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1110"/>
+    </row>
+    <row r="1111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1111"/>
+    </row>
+    <row r="1112" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1112"/>
+    </row>
+    <row r="1113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1113"/>
+    </row>
+    <row r="1114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1114"/>
+    </row>
+    <row r="1115" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1115"/>
+    </row>
+    <row r="1116" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1116"/>
+    </row>
+    <row r="1117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1117"/>
+    </row>
+    <row r="1118" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1118"/>
+    </row>
+    <row r="1119" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1119"/>
+    </row>
+    <row r="1120" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1120"/>
+    </row>
+    <row r="1121" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1121"/>
+    </row>
+    <row r="1122" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1122"/>
+    </row>
+    <row r="1123" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1123"/>
+    </row>
+    <row r="1124" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1124"/>
+    </row>
+    <row r="1125" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1125"/>
+    </row>
+    <row r="1126" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1126"/>
+    </row>
+    <row r="1127" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1127"/>
+    </row>
+    <row r="1128" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1128"/>
+    </row>
+    <row r="1129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1129"/>
+    </row>
+    <row r="1130" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1130"/>
+    </row>
+    <row r="1131" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1131"/>
+    </row>
+    <row r="1132" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1132"/>
+    </row>
+    <row r="1133" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1133"/>
+    </row>
+    <row r="1134" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1134"/>
+    </row>
+    <row r="1135" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1135"/>
+    </row>
+    <row r="1136" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1136"/>
+    </row>
+    <row r="1137" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1137"/>
+    </row>
+    <row r="1138" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1138"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
